--- a/Pricing Logic/modules/manual/cart_rules_704_chunk_2.xlsx
+++ b/Pricing Logic/modules/manual/cart_rules_704_chunk_2.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,219 +396,219 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>24245</v>
+        <v>25856</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>24246</v>
+        <v>25857</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>24246</v>
+        <v>25859</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>24247</v>
+        <v>25860</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>24247</v>
+        <v>25861</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>24248</v>
+        <v>25866</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>24248</v>
+        <v>25873</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>24252</v>
+        <v>25874</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>24253</v>
+        <v>25875</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>24254</v>
+        <v>25876</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>24254</v>
+        <v>25893</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>24256</v>
+        <v>25899</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>24257</v>
+        <v>25906</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>24258</v>
+        <v>25907</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>24260</v>
+        <v>25910</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>24378</v>
+        <v>25958</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>24566</v>
+        <v>25959</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>24567</v>
+        <v>25960</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>24618</v>
+        <v>25991</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>24618</v>
+        <v>25991</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -616,10 +616,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>24619</v>
+        <v>25992</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -627,21 +627,21 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>24619</v>
+        <v>25992</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>24620</v>
+        <v>25994</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -649,21 +649,21 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>24620</v>
+        <v>25994</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>24621</v>
+        <v>25995</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -671,29 +671,29 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>24621</v>
+        <v>25995</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>24622</v>
+        <v>26028</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>24622</v>
+        <v>26028</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -704,21 +704,21 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>24623</v>
+        <v>26062</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>24623</v>
+        <v>26062</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>24624</v>
+        <v>26063</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -737,43 +737,43 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>24624</v>
+        <v>26063</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>24625</v>
+        <v>26065</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>24625</v>
+        <v>26124</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>24626</v>
+        <v>26124</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -781,21 +781,21 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>24626</v>
+        <v>26125</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>24627</v>
+        <v>26125</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -803,18 +803,18 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>24627</v>
+        <v>26126</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>24629</v>
+        <v>26126</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -825,18 +825,18 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>24667</v>
+        <v>26127</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>24668</v>
+        <v>26127</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -847,62 +847,62 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>24669</v>
+        <v>26128</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>24670</v>
+        <v>26128</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>24707</v>
+        <v>26189</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>24707</v>
+        <v>26190</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>24708</v>
+        <v>26223</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>24708</v>
+        <v>26223</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -913,21 +913,21 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>24709</v>
+        <v>26224</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>24709</v>
+        <v>26224</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -935,18 +935,18 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>24711</v>
+        <v>26226</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>24711</v>
+        <v>26226</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>24712</v>
+        <v>26227</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -968,21 +968,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>24712</v>
+        <v>26227</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>24713</v>
+        <v>26228</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -990,21 +990,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>24713</v>
+        <v>26228</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>24715</v>
+        <v>26229</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1012,32 +1012,32 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>24715</v>
+        <v>26229</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>24722</v>
+        <v>26354</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>24723</v>
+        <v>26354</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -1045,32 +1045,32 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>24724</v>
+        <v>26355</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C61">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>24725</v>
+        <v>26355</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>24726</v>
+        <v>26357</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -1078,255 +1078,35 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>24727</v>
+        <v>26357</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C64">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>24728</v>
+        <v>26553</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>24729</v>
+        <v>26594</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>24731</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>24732</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>25251</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
-      </c>
-      <c r="C69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>25251</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>25252</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>25252</v>
-      </c>
-      <c r="B72">
-        <v>3</v>
-      </c>
-      <c r="C72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>25253</v>
-      </c>
-      <c r="B73">
-        <v>3</v>
-      </c>
-      <c r="C73">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
-        <v>25253</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75">
-        <v>25254</v>
-      </c>
-      <c r="B75">
-        <v>3</v>
-      </c>
-      <c r="C75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76">
-        <v>25254</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77">
-        <v>25255</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78">
-        <v>25278</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79">
-        <v>25286</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80">
-        <v>25287</v>
-      </c>
-      <c r="B80">
-        <v>3</v>
-      </c>
-      <c r="C80">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81">
-        <v>25287</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82">
-        <v>25288</v>
-      </c>
-      <c r="B82">
-        <v>3</v>
-      </c>
-      <c r="C82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83">
-        <v>25288</v>
-      </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84">
-        <v>25289</v>
-      </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85">
-        <v>25289</v>
-      </c>
-      <c r="B85">
-        <v>3</v>
-      </c>
-      <c r="C85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86">
-        <v>25378</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
